--- a/docs/templates/hooslog_week_plan_template.xlsx
+++ b/docs/templates/hooslog_week_plan_template.xlsx
@@ -696,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1088,12 +1088,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Brenden Michael McMahon</t>
+          <t>Andrew Tyler Mangum</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>zwh3ga@virginia.edu</t>
+          <t>utb5vp@virginia.edu</t>
         </is>
       </c>
       <c r="C22" s="12" t="n"/>
@@ -1103,12 +1103,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Eric Moore</t>
+          <t>Brenden Michael McMahon</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>zqu3wh@virginia.edu</t>
+          <t>zwh3ga@virginia.edu</t>
         </is>
       </c>
       <c r="C23" s="12" t="n"/>
@@ -1118,12 +1118,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Richard Charles Moreno</t>
+          <t>Eric Moore</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>jxm8cj@virginia.edu</t>
+          <t>zqu3wh@virginia.edu</t>
         </is>
       </c>
       <c r="C24" s="12" t="n"/>
@@ -1133,12 +1133,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Sam John Palmer</t>
+          <t>Richard Charles Moreno</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>vwz2at@virginia.edu</t>
+          <t>jxm8cj@virginia.edu</t>
         </is>
       </c>
       <c r="C25" s="12" t="n"/>
@@ -1148,12 +1148,12 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Charles Perry</t>
+          <t>Sam John Palmer</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>ghu7yg@virginia.edu</t>
+          <t>vwz2at@virginia.edu</t>
         </is>
       </c>
       <c r="C26" s="12" t="n"/>
@@ -1163,12 +1163,12 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Pierce Conor Seigne</t>
+          <t>Charles Perry</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>xrk9rs@virginia.edu</t>
+          <t>ghu7yg@virginia.edu</t>
         </is>
       </c>
       <c r="C27" s="12" t="n"/>
@@ -1178,12 +1178,12 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Jonathan Logan Seyfert</t>
+          <t>Pierce Conor Seigne</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>mea6wq@virginia.edu</t>
+          <t>xrk9rs@virginia.edu</t>
         </is>
       </c>
       <c r="C28" s="12" t="n"/>
@@ -1193,12 +1193,12 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>William Hayden Sheets</t>
+          <t>Jonathan Logan Seyfert</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>fnh4mv@virginia.edu</t>
+          <t>mea6wq@virginia.edu</t>
         </is>
       </c>
       <c r="C29" s="12" t="n"/>
@@ -1208,12 +1208,12 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Alexander J Valencia</t>
+          <t>William Hayden Sheets</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>nrk7dj@virginia.edu</t>
+          <t>fnh4mv@virginia.edu</t>
         </is>
       </c>
       <c r="C30" s="12" t="n"/>
@@ -1223,42 +1223,57 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Jimmy Wischusen</t>
+          <t>Alexander J Valencia</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>kna3ed@virginia.edu</t>
+          <t>nrk7dj@virginia.edu</t>
         </is>
       </c>
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="13" t="n"/>
       <c r="E31" s="12" t="n"/>
     </row>
-    <row r="33">
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Mid-D:</t>
-        </is>
-      </c>
-      <c r="H33" s="14">
-        <f>COUNTIF($D$2:$D$31,"Mid-D")</f>
-        <v/>
-      </c>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Jimmy Wischusen</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>kna3ed@virginia.edu</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>Mid-D:</t>
+        </is>
+      </c>
+      <c r="H34" s="14">
+        <f>COUNTIF($D$2:$D$32,"Mid-D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>Distance:</t>
         </is>
       </c>
-      <c r="H34" s="14">
-        <f>COUNTIF($D$2:$D$31,"Distance")</f>
+      <c r="H35" s="14">
+        <f>COUNTIF($D$2:$D$32,"Distance")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="G35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Blank group cells aren't counted — those guys stay where they were.</t>
         </is>
@@ -1266,7 +1281,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Distance or Mid-D" error="Type Distance or Mid-D, or leave it blank." promptTitle="Training group" prompt="Distance or Mid-D. Leave blank to keep the athlete where they already are." type="list">
+    <dataValidation sqref="D2:D32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Distance or Mid-D" error="Type Distance or Mid-D, or leave it blank." promptTitle="Training group" prompt="Distance or Mid-D. Leave blank to keep the athlete where they already are." type="list">
       <formula1>"Distance,Mid-D"</formula1>
     </dataValidation>
   </dataValidations>
